--- a/(枠)◯年度一式/管理月報/管理月報04.xlsx
+++ b/(枠)◯年度一式/管理月報/管理月報04.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\layhi\OneDrive\ドキュメント\日報月報他\(枠)◯年度一式\管理月報\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F17EB889-A460-4776-89CD-CA1133305692}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D64F588-8D93-437F-A7B0-2E5B1DCFD696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="165" yWindow="0" windowWidth="18435" windowHeight="15480" tabRatio="848" xr2:uid="{C3BF799E-CCDA-4119-9ED7-C2C914663A17}"/>
+    <workbookView xWindow="7995" yWindow="765" windowWidth="18615" windowHeight="14715" tabRatio="848" xr2:uid="{C3BF799E-CCDA-4119-9ED7-C2C914663A17}"/>
   </bookViews>
   <sheets>
     <sheet name="A-1" sheetId="1" r:id="rId1"/>
@@ -3256,6 +3256,9 @@
     <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="187" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3417,9 +3420,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3922,89 +3922,89 @@
     <row r="2" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="3" spans="1:18" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="4" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="143" t="s">
+      <c r="A4" s="144" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="143"/>
-      <c r="C4" s="143"/>
-      <c r="D4" s="143"/>
-      <c r="E4" s="143"/>
-      <c r="F4" s="143"/>
-      <c r="G4" s="143"/>
-      <c r="H4" s="143"/>
-      <c r="I4" s="143"/>
-      <c r="J4" s="143"/>
-      <c r="K4" s="143"/>
-      <c r="L4" s="143"/>
-      <c r="M4" s="143"/>
-      <c r="N4" s="143"/>
-      <c r="O4" s="143"/>
-      <c r="P4" s="143"/>
-      <c r="Q4" s="143"/>
-      <c r="R4" s="143"/>
+      <c r="B4" s="144"/>
+      <c r="C4" s="144"/>
+      <c r="D4" s="144"/>
+      <c r="E4" s="144"/>
+      <c r="F4" s="144"/>
+      <c r="G4" s="144"/>
+      <c r="H4" s="144"/>
+      <c r="I4" s="144"/>
+      <c r="J4" s="144"/>
+      <c r="K4" s="144"/>
+      <c r="L4" s="144"/>
+      <c r="M4" s="144"/>
+      <c r="N4" s="144"/>
+      <c r="O4" s="144"/>
+      <c r="P4" s="144"/>
+      <c r="Q4" s="144"/>
+      <c r="R4" s="144"/>
     </row>
     <row r="5" spans="1:18" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2"/>
-      <c r="I5" s="144" t="s">
+      <c r="I5" s="145" t="s">
         <v>32</v>
       </c>
-      <c r="J5" s="144"/>
-      <c r="K5" s="144" t="s">
+      <c r="J5" s="145"/>
+      <c r="K5" s="145" t="s">
         <v>30</v>
       </c>
-      <c r="L5" s="144"/>
-      <c r="M5" s="144"/>
-      <c r="N5" s="144"/>
-      <c r="O5" s="144" t="s">
+      <c r="L5" s="145"/>
+      <c r="M5" s="145"/>
+      <c r="N5" s="145"/>
+      <c r="O5" s="145" t="s">
         <v>69</v>
       </c>
-      <c r="P5" s="144"/>
-      <c r="Q5" s="145" t="s">
+      <c r="P5" s="145"/>
+      <c r="Q5" s="146" t="s">
         <v>26</v>
       </c>
-      <c r="R5" s="146"/>
+      <c r="R5" s="147"/>
     </row>
     <row r="6" spans="1:18" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2"/>
-      <c r="I6" s="144" t="s">
+      <c r="I6" s="145" t="s">
         <v>71</v>
       </c>
-      <c r="J6" s="144"/>
-      <c r="K6" s="144" t="s">
+      <c r="J6" s="145"/>
+      <c r="K6" s="145" t="s">
         <v>31</v>
       </c>
-      <c r="L6" s="144"/>
-      <c r="M6" s="144"/>
-      <c r="N6" s="144"/>
-      <c r="O6" s="144" t="s">
+      <c r="L6" s="145"/>
+      <c r="M6" s="145"/>
+      <c r="N6" s="145"/>
+      <c r="O6" s="145" t="s">
         <v>70</v>
       </c>
-      <c r="P6" s="144"/>
-      <c r="Q6" s="144" t="s">
+      <c r="P6" s="145"/>
+      <c r="Q6" s="145" t="s">
         <v>27</v>
       </c>
-      <c r="R6" s="144"/>
+      <c r="R6" s="145"/>
     </row>
     <row r="7" spans="1:18" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2"/>
-      <c r="I7" s="144" t="s">
+      <c r="I7" s="145" t="s">
         <v>33</v>
       </c>
-      <c r="J7" s="144"/>
-      <c r="K7" s="152" t="s">
+      <c r="J7" s="145"/>
+      <c r="K7" s="153" t="s">
         <v>196</v>
       </c>
-      <c r="L7" s="144"/>
-      <c r="M7" s="144"/>
-      <c r="N7" s="144"/>
-      <c r="O7" s="144" t="s">
+      <c r="L7" s="145"/>
+      <c r="M7" s="145"/>
+      <c r="N7" s="145"/>
+      <c r="O7" s="145" t="s">
         <v>29</v>
       </c>
-      <c r="P7" s="144"/>
-      <c r="Q7" s="144" t="s">
+      <c r="P7" s="145"/>
+      <c r="Q7" s="145" t="s">
         <v>28</v>
       </c>
-      <c r="R7" s="144"/>
+      <c r="R7" s="145"/>
     </row>
     <row r="8" spans="1:18" s="3" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2"/>
@@ -4023,13 +4023,13 @@
       <c r="A9" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="150" t="str">
+      <c r="B9" s="151" t="str">
         <f>"("&amp;TEXT(DATE(E9, 4, 1), "ggge年mm月")&amp;")"</f>
         <v>(令和9年04月)</v>
       </c>
-      <c r="C9" s="150"/>
-      <c r="D9" s="151"/>
-      <c r="E9" s="197">
+      <c r="C9" s="151"/>
+      <c r="D9" s="152"/>
+      <c r="E9" s="143">
         <v>2027</v>
       </c>
     </row>
@@ -4073,13 +4073,13 @@
       <c r="M10" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="N10" s="147" t="s">
+      <c r="N10" s="148" t="s">
         <v>24</v>
       </c>
-      <c r="O10" s="148"/>
-      <c r="P10" s="148"/>
-      <c r="Q10" s="148"/>
-      <c r="R10" s="149"/>
+      <c r="O10" s="149"/>
+      <c r="P10" s="149"/>
+      <c r="Q10" s="149"/>
+      <c r="R10" s="150"/>
     </row>
     <row r="11" spans="1:18" s="38" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="93"/>
@@ -5260,30 +5260,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="18.75" x14ac:dyDescent="0.15">
-      <c r="A1" s="192" t="s">
+      <c r="A1" s="193" t="s">
         <v>145</v>
       </c>
-      <c r="B1" s="192"/>
-      <c r="C1" s="192"/>
-      <c r="D1" s="192"/>
-      <c r="E1" s="192"/>
-      <c r="F1" s="192"/>
-      <c r="G1" s="192"/>
-      <c r="H1" s="192"/>
-      <c r="I1" s="192"/>
-      <c r="J1" s="192"/>
-      <c r="K1" s="192"/>
-      <c r="L1" s="192"/>
-      <c r="M1" s="192"/>
-      <c r="N1" s="192"/>
-      <c r="O1" s="192"/>
-      <c r="P1" s="192"/>
-      <c r="Q1" s="192"/>
-      <c r="R1" s="192"/>
-      <c r="S1" s="192"/>
-      <c r="T1" s="192"/>
-      <c r="U1" s="192"/>
-      <c r="V1" s="192"/>
+      <c r="B1" s="193"/>
+      <c r="C1" s="193"/>
+      <c r="D1" s="193"/>
+      <c r="E1" s="193"/>
+      <c r="F1" s="193"/>
+      <c r="G1" s="193"/>
+      <c r="H1" s="193"/>
+      <c r="I1" s="193"/>
+      <c r="J1" s="193"/>
+      <c r="K1" s="193"/>
+      <c r="L1" s="193"/>
+      <c r="M1" s="193"/>
+      <c r="N1" s="193"/>
+      <c r="O1" s="193"/>
+      <c r="P1" s="193"/>
+      <c r="Q1" s="193"/>
+      <c r="R1" s="193"/>
+      <c r="S1" s="193"/>
+      <c r="T1" s="193"/>
+      <c r="U1" s="193"/>
+      <c r="V1" s="193"/>
     </row>
     <row r="2" spans="1:22" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="3" spans="1:22" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -5293,44 +5293,44 @@
     <row r="7" spans="1:22" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="8" spans="1:22" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="9" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="150" t="str">
+      <c r="B9" s="151" t="str">
         <f>'A-1'!B9:D9</f>
         <v>(令和9年04月)</v>
       </c>
-      <c r="C9" s="150"/>
-      <c r="D9" s="151"/>
+      <c r="C9" s="151"/>
+      <c r="D9" s="152"/>
     </row>
     <row r="10" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="102"/>
-      <c r="B10" s="189" t="s">
+      <c r="B10" s="190" t="s">
         <v>146</v>
       </c>
-      <c r="C10" s="190"/>
-      <c r="D10" s="190"/>
-      <c r="E10" s="190"/>
-      <c r="F10" s="191"/>
-      <c r="G10" s="189" t="s">
+      <c r="C10" s="191"/>
+      <c r="D10" s="191"/>
+      <c r="E10" s="191"/>
+      <c r="F10" s="192"/>
+      <c r="G10" s="190" t="s">
         <v>147</v>
       </c>
-      <c r="H10" s="190"/>
-      <c r="I10" s="190"/>
-      <c r="J10" s="190"/>
-      <c r="K10" s="191"/>
+      <c r="H10" s="191"/>
+      <c r="I10" s="191"/>
+      <c r="J10" s="191"/>
+      <c r="K10" s="192"/>
       <c r="L10" s="102"/>
-      <c r="M10" s="189" t="s">
+      <c r="M10" s="190" t="s">
         <v>159</v>
       </c>
-      <c r="N10" s="190"/>
-      <c r="O10" s="190"/>
-      <c r="P10" s="190"/>
-      <c r="Q10" s="191"/>
-      <c r="R10" s="189" t="s">
+      <c r="N10" s="191"/>
+      <c r="O10" s="191"/>
+      <c r="P10" s="191"/>
+      <c r="Q10" s="192"/>
+      <c r="R10" s="190" t="s">
         <v>148</v>
       </c>
-      <c r="S10" s="190"/>
-      <c r="T10" s="190"/>
-      <c r="U10" s="190"/>
-      <c r="V10" s="191"/>
+      <c r="S10" s="191"/>
+      <c r="T10" s="191"/>
+      <c r="U10" s="191"/>
+      <c r="V10" s="192"/>
     </row>
     <row r="11" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="47" t="s">
@@ -6770,34 +6770,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18.75" x14ac:dyDescent="0.15">
-      <c r="A1" s="192" t="s">
+      <c r="A1" s="193" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="192"/>
-      <c r="C1" s="192"/>
-      <c r="D1" s="192"/>
-      <c r="E1" s="192"/>
-      <c r="F1" s="192"/>
-      <c r="G1" s="192"/>
-      <c r="H1" s="192"/>
-      <c r="I1" s="192"/>
-      <c r="J1" s="192"/>
-      <c r="K1" s="192"/>
-      <c r="L1" s="192"/>
-      <c r="M1" s="192"/>
-      <c r="N1" s="192"/>
-      <c r="O1" s="192"/>
-      <c r="P1" s="192"/>
-      <c r="Q1" s="192"/>
-      <c r="R1" s="192"/>
-      <c r="S1" s="192"/>
-      <c r="T1" s="192"/>
-      <c r="U1" s="192"/>
-      <c r="V1" s="192"/>
-      <c r="W1" s="192"/>
-      <c r="X1" s="192"/>
-      <c r="Y1" s="192"/>
-      <c r="Z1" s="192"/>
+      <c r="B1" s="193"/>
+      <c r="C1" s="193"/>
+      <c r="D1" s="193"/>
+      <c r="E1" s="193"/>
+      <c r="F1" s="193"/>
+      <c r="G1" s="193"/>
+      <c r="H1" s="193"/>
+      <c r="I1" s="193"/>
+      <c r="J1" s="193"/>
+      <c r="K1" s="193"/>
+      <c r="L1" s="193"/>
+      <c r="M1" s="193"/>
+      <c r="N1" s="193"/>
+      <c r="O1" s="193"/>
+      <c r="P1" s="193"/>
+      <c r="Q1" s="193"/>
+      <c r="R1" s="193"/>
+      <c r="S1" s="193"/>
+      <c r="T1" s="193"/>
+      <c r="U1" s="193"/>
+      <c r="V1" s="193"/>
+      <c r="W1" s="193"/>
+      <c r="X1" s="193"/>
+      <c r="Y1" s="193"/>
+      <c r="Z1" s="193"/>
     </row>
     <row r="2" spans="1:26" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="3" spans="1:26" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -6807,53 +6807,53 @@
     <row r="7" spans="1:26" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="8" spans="1:26" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="9" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="150" t="str">
+      <c r="B9" s="151" t="str">
         <f>'A-1'!B9:D9</f>
         <v>(令和9年04月)</v>
       </c>
-      <c r="C9" s="150"/>
-      <c r="D9" s="151"/>
-      <c r="G9" s="150"/>
-      <c r="H9" s="150"/>
-      <c r="I9" s="151"/>
+      <c r="C9" s="151"/>
+      <c r="D9" s="152"/>
+      <c r="G9" s="151"/>
+      <c r="H9" s="151"/>
+      <c r="I9" s="152"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="102"/>
-      <c r="B10" s="189" t="s">
+      <c r="B10" s="190" t="s">
         <v>143</v>
       </c>
-      <c r="C10" s="190"/>
-      <c r="D10" s="190"/>
-      <c r="E10" s="190"/>
-      <c r="F10" s="191"/>
-      <c r="G10" s="189" t="s">
+      <c r="C10" s="191"/>
+      <c r="D10" s="191"/>
+      <c r="E10" s="191"/>
+      <c r="F10" s="192"/>
+      <c r="G10" s="190" t="s">
         <v>141</v>
       </c>
-      <c r="H10" s="190"/>
-      <c r="I10" s="190"/>
-      <c r="J10" s="190"/>
-      <c r="K10" s="191"/>
-      <c r="L10" s="189" t="s">
+      <c r="H10" s="191"/>
+      <c r="I10" s="191"/>
+      <c r="J10" s="191"/>
+      <c r="K10" s="192"/>
+      <c r="L10" s="190" t="s">
         <v>103</v>
       </c>
-      <c r="M10" s="190"/>
-      <c r="N10" s="190"/>
-      <c r="O10" s="190"/>
-      <c r="P10" s="191"/>
-      <c r="Q10" s="189" t="s">
+      <c r="M10" s="191"/>
+      <c r="N10" s="191"/>
+      <c r="O10" s="191"/>
+      <c r="P10" s="192"/>
+      <c r="Q10" s="190" t="s">
         <v>142</v>
       </c>
-      <c r="R10" s="190"/>
-      <c r="S10" s="190"/>
-      <c r="T10" s="190"/>
-      <c r="U10" s="191"/>
-      <c r="V10" s="189" t="s">
+      <c r="R10" s="191"/>
+      <c r="S10" s="191"/>
+      <c r="T10" s="191"/>
+      <c r="U10" s="192"/>
+      <c r="V10" s="190" t="s">
         <v>91</v>
       </c>
-      <c r="W10" s="190"/>
-      <c r="X10" s="190"/>
-      <c r="Y10" s="190"/>
-      <c r="Z10" s="191"/>
+      <c r="W10" s="191"/>
+      <c r="X10" s="191"/>
+      <c r="Y10" s="191"/>
+      <c r="Z10" s="192"/>
     </row>
     <row r="11" spans="1:26" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="47" t="s">
@@ -8476,32 +8476,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="24" x14ac:dyDescent="0.15">
-      <c r="A1" s="193" t="s">
+      <c r="A1" s="194" t="s">
         <v>92</v>
       </c>
-      <c r="B1" s="193"/>
-      <c r="C1" s="193"/>
-      <c r="D1" s="193"/>
-      <c r="E1" s="193"/>
-      <c r="F1" s="193"/>
-      <c r="G1" s="193"/>
-      <c r="H1" s="193"/>
-      <c r="I1" s="193"/>
-      <c r="J1" s="193"/>
-      <c r="K1" s="193"/>
-      <c r="L1" s="193"/>
-      <c r="M1" s="193"/>
-      <c r="N1" s="193"/>
-      <c r="O1" s="193"/>
-      <c r="P1" s="193"/>
-      <c r="Q1" s="193"/>
-      <c r="R1" s="193"/>
-      <c r="S1" s="193"/>
-      <c r="T1" s="193"/>
-      <c r="U1" s="193"/>
-      <c r="V1" s="193"/>
-      <c r="W1" s="193"/>
-      <c r="X1" s="193"/>
+      <c r="B1" s="194"/>
+      <c r="C1" s="194"/>
+      <c r="D1" s="194"/>
+      <c r="E1" s="194"/>
+      <c r="F1" s="194"/>
+      <c r="G1" s="194"/>
+      <c r="H1" s="194"/>
+      <c r="I1" s="194"/>
+      <c r="J1" s="194"/>
+      <c r="K1" s="194"/>
+      <c r="L1" s="194"/>
+      <c r="M1" s="194"/>
+      <c r="N1" s="194"/>
+      <c r="O1" s="194"/>
+      <c r="P1" s="194"/>
+      <c r="Q1" s="194"/>
+      <c r="R1" s="194"/>
+      <c r="S1" s="194"/>
+      <c r="T1" s="194"/>
+      <c r="U1" s="194"/>
+      <c r="V1" s="194"/>
+      <c r="W1" s="194"/>
+      <c r="X1" s="194"/>
     </row>
     <row r="2" spans="1:24" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="3" spans="1:24" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -8511,48 +8511,48 @@
     <row r="7" spans="1:24" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="8" spans="1:24" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="9" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="150" t="str">
+      <c r="B9" s="151" t="str">
         <f>'A-1'!B9:D9</f>
         <v>(令和9年04月)</v>
       </c>
-      <c r="C9" s="150"/>
-      <c r="D9" s="151"/>
+      <c r="C9" s="151"/>
+      <c r="D9" s="152"/>
     </row>
     <row r="10" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="102"/>
-      <c r="B10" s="189" t="s">
+      <c r="B10" s="190" t="s">
         <v>180</v>
       </c>
-      <c r="C10" s="190"/>
-      <c r="D10" s="190"/>
-      <c r="E10" s="190"/>
-      <c r="F10" s="191"/>
-      <c r="G10" s="189" t="s">
+      <c r="C10" s="191"/>
+      <c r="D10" s="191"/>
+      <c r="E10" s="191"/>
+      <c r="F10" s="192"/>
+      <c r="G10" s="190" t="s">
         <v>181</v>
       </c>
-      <c r="H10" s="190"/>
-      <c r="I10" s="190"/>
-      <c r="J10" s="190"/>
-      <c r="K10" s="191"/>
-      <c r="L10" s="159" t="s">
+      <c r="H10" s="191"/>
+      <c r="I10" s="191"/>
+      <c r="J10" s="191"/>
+      <c r="K10" s="192"/>
+      <c r="L10" s="160" t="s">
         <v>161</v>
       </c>
-      <c r="M10" s="159"/>
-      <c r="N10" s="159"/>
-      <c r="O10" s="159"/>
-      <c r="P10" s="159"/>
-      <c r="Q10" s="189" t="s">
+      <c r="M10" s="160"/>
+      <c r="N10" s="160"/>
+      <c r="O10" s="160"/>
+      <c r="P10" s="160"/>
+      <c r="Q10" s="190" t="s">
         <v>182</v>
       </c>
-      <c r="R10" s="190"/>
-      <c r="S10" s="190"/>
-      <c r="T10" s="190"/>
-      <c r="U10" s="191"/>
-      <c r="V10" s="194" t="s">
+      <c r="R10" s="191"/>
+      <c r="S10" s="191"/>
+      <c r="T10" s="191"/>
+      <c r="U10" s="192"/>
+      <c r="V10" s="195" t="s">
         <v>183</v>
       </c>
-      <c r="W10" s="195"/>
-      <c r="X10" s="196"/>
+      <c r="W10" s="196"/>
+      <c r="X10" s="197"/>
     </row>
     <row r="11" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="47" t="s">
@@ -9994,22 +9994,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="25.5" x14ac:dyDescent="0.15">
-      <c r="A1" s="143" t="s">
+      <c r="A1" s="144" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="143"/>
-      <c r="G1" s="143"/>
-      <c r="H1" s="143"/>
-      <c r="I1" s="143"/>
-      <c r="J1" s="143"/>
-      <c r="K1" s="143"/>
-      <c r="L1" s="143"/>
-      <c r="M1" s="143"/>
-      <c r="N1" s="143"/>
+      <c r="B1" s="144"/>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
+      <c r="F1" s="144"/>
+      <c r="G1" s="144"/>
+      <c r="H1" s="144"/>
+      <c r="I1" s="144"/>
+      <c r="J1" s="144"/>
+      <c r="K1" s="144"/>
+      <c r="L1" s="144"/>
+      <c r="M1" s="144"/>
+      <c r="N1" s="144"/>
       <c r="O1" s="98"/>
       <c r="P1" s="98"/>
     </row>
@@ -10032,63 +10032,63 @@
     </row>
     <row r="5" spans="1:16" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="2"/>
-      <c r="F5" s="159" t="s">
+      <c r="F5" s="160" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="159"/>
-      <c r="H5" s="159" t="s">
+      <c r="G5" s="160"/>
+      <c r="H5" s="160" t="s">
         <v>30</v>
       </c>
-      <c r="I5" s="159"/>
-      <c r="J5" s="159" t="s">
+      <c r="I5" s="160"/>
+      <c r="J5" s="160" t="s">
         <v>72</v>
       </c>
-      <c r="K5" s="159"/>
-      <c r="L5" s="159" t="s">
+      <c r="K5" s="160"/>
+      <c r="L5" s="160" t="s">
         <v>36</v>
       </c>
-      <c r="M5" s="159"/>
-      <c r="N5" s="159"/>
+      <c r="M5" s="160"/>
+      <c r="N5" s="160"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A6" s="2"/>
-      <c r="F6" s="159" t="s">
+      <c r="F6" s="160" t="s">
         <v>74</v>
       </c>
-      <c r="G6" s="159"/>
-      <c r="H6" s="153" t="s">
+      <c r="G6" s="160"/>
+      <c r="H6" s="154" t="s">
         <v>31</v>
       </c>
-      <c r="I6" s="155"/>
-      <c r="J6" s="159" t="s">
+      <c r="I6" s="156"/>
+      <c r="J6" s="160" t="s">
         <v>73</v>
       </c>
-      <c r="K6" s="159"/>
-      <c r="L6" s="159" t="s">
+      <c r="K6" s="160"/>
+      <c r="L6" s="160" t="s">
         <v>37</v>
       </c>
-      <c r="M6" s="159"/>
-      <c r="N6" s="159"/>
+      <c r="M6" s="160"/>
+      <c r="N6" s="160"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A7" s="2"/>
-      <c r="F7" s="159" t="s">
+      <c r="F7" s="160" t="s">
         <v>33</v>
       </c>
-      <c r="G7" s="159"/>
-      <c r="H7" s="159" t="s">
+      <c r="G7" s="160"/>
+      <c r="H7" s="160" t="s">
         <v>196</v>
       </c>
-      <c r="I7" s="159"/>
-      <c r="J7" s="159" t="s">
+      <c r="I7" s="160"/>
+      <c r="J7" s="160" t="s">
         <v>29</v>
       </c>
-      <c r="K7" s="159"/>
-      <c r="L7" s="159" t="s">
+      <c r="K7" s="160"/>
+      <c r="L7" s="160" t="s">
         <v>38</v>
       </c>
-      <c r="M7" s="159"/>
-      <c r="N7" s="159"/>
+      <c r="M7" s="160"/>
+      <c r="N7" s="160"/>
     </row>
     <row r="8" spans="1:16" hidden="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2"/>
@@ -10106,12 +10106,12 @@
       <c r="A9" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B9" s="150" t="str">
+      <c r="B9" s="151" t="str">
         <f>'A-1'!B9:D9</f>
         <v>(令和9年04月)</v>
       </c>
-      <c r="C9" s="150"/>
-      <c r="D9" s="151"/>
+      <c r="C9" s="151"/>
+      <c r="D9" s="152"/>
     </row>
     <row r="10" spans="1:16" s="40" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="45" t="s">
@@ -10123,14 +10123,14 @@
       <c r="C10" s="48" t="s">
         <v>50</v>
       </c>
-      <c r="D10" s="153" t="s">
+      <c r="D10" s="154" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="154"/>
-      <c r="F10" s="154"/>
-      <c r="G10" s="154"/>
-      <c r="H10" s="154"/>
-      <c r="I10" s="155"/>
+      <c r="E10" s="155"/>
+      <c r="F10" s="155"/>
+      <c r="G10" s="155"/>
+      <c r="H10" s="155"/>
+      <c r="I10" s="156"/>
       <c r="J10" s="39" t="s">
         <v>13</v>
       </c>
@@ -10140,10 +10140,10 @@
       <c r="L10" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="M10" s="153" t="s">
+      <c r="M10" s="154" t="s">
         <v>42</v>
       </c>
-      <c r="N10" s="155"/>
+      <c r="N10" s="156"/>
     </row>
     <row r="11" spans="1:16" s="40" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="46"/>
@@ -10153,16 +10153,16 @@
       <c r="C11" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="153" t="s">
+      <c r="D11" s="154" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="154"/>
-      <c r="F11" s="155"/>
-      <c r="G11" s="156" t="s">
+      <c r="E11" s="155"/>
+      <c r="F11" s="156"/>
+      <c r="G11" s="157" t="s">
         <v>101</v>
       </c>
-      <c r="H11" s="157"/>
-      <c r="I11" s="158"/>
+      <c r="H11" s="158"/>
+      <c r="I11" s="159"/>
       <c r="J11" s="41" t="s">
         <v>14</v>
       </c>
@@ -11116,149 +11116,149 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" s="100" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="160" t="s">
+      <c r="A1" s="161" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="160"/>
-      <c r="C1" s="160"/>
-      <c r="D1" s="160"/>
-      <c r="E1" s="160"/>
-      <c r="F1" s="160"/>
-      <c r="G1" s="160"/>
-      <c r="H1" s="160"/>
-      <c r="I1" s="160"/>
-      <c r="J1" s="160"/>
-      <c r="K1" s="160"/>
-      <c r="L1" s="160"/>
-      <c r="M1" s="160"/>
-      <c r="N1" s="160"/>
-      <c r="O1" s="160"/>
-      <c r="P1" s="160"/>
-      <c r="Q1" s="160"/>
-      <c r="R1" s="160"/>
-      <c r="S1" s="160"/>
-      <c r="T1" s="160"/>
-      <c r="U1" s="160"/>
-      <c r="V1" s="160"/>
+      <c r="B1" s="161"/>
+      <c r="C1" s="161"/>
+      <c r="D1" s="161"/>
+      <c r="E1" s="161"/>
+      <c r="F1" s="161"/>
+      <c r="G1" s="161"/>
+      <c r="H1" s="161"/>
+      <c r="I1" s="161"/>
+      <c r="J1" s="161"/>
+      <c r="K1" s="161"/>
+      <c r="L1" s="161"/>
+      <c r="M1" s="161"/>
+      <c r="N1" s="161"/>
+      <c r="O1" s="161"/>
+      <c r="P1" s="161"/>
+      <c r="Q1" s="161"/>
+      <c r="R1" s="161"/>
+      <c r="S1" s="161"/>
+      <c r="T1" s="161"/>
+      <c r="U1" s="161"/>
+      <c r="V1" s="161"/>
     </row>
     <row r="2" spans="1:22" s="44" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="H2" s="166" t="s">
+      <c r="H2" s="167" t="s">
         <v>32</v>
       </c>
-      <c r="I2" s="167"/>
-      <c r="J2" s="168" t="s">
+      <c r="I2" s="168"/>
+      <c r="J2" s="169" t="s">
         <v>30</v>
       </c>
-      <c r="K2" s="169"/>
-      <c r="L2" s="170"/>
-      <c r="M2" s="166" t="s">
+      <c r="K2" s="170"/>
+      <c r="L2" s="171"/>
+      <c r="M2" s="167" t="s">
         <v>75</v>
       </c>
-      <c r="N2" s="171"/>
-      <c r="O2" s="167"/>
-      <c r="P2" s="168" t="s">
+      <c r="N2" s="172"/>
+      <c r="O2" s="168"/>
+      <c r="P2" s="169" t="s">
         <v>170</v>
       </c>
-      <c r="Q2" s="169"/>
-      <c r="R2" s="169"/>
-      <c r="S2" s="169"/>
-      <c r="T2" s="170"/>
+      <c r="Q2" s="170"/>
+      <c r="R2" s="170"/>
+      <c r="S2" s="170"/>
+      <c r="T2" s="171"/>
     </row>
     <row r="3" spans="1:22" s="44" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="H3" s="166" t="s">
+      <c r="H3" s="167" t="s">
         <v>78</v>
       </c>
-      <c r="I3" s="167"/>
-      <c r="J3" s="168" t="s">
+      <c r="I3" s="168"/>
+      <c r="J3" s="169" t="s">
         <v>174</v>
       </c>
-      <c r="K3" s="169"/>
-      <c r="L3" s="170"/>
-      <c r="M3" s="166" t="s">
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="167" t="s">
         <v>76</v>
       </c>
-      <c r="N3" s="171"/>
-      <c r="O3" s="167"/>
-      <c r="P3" s="168" t="s">
+      <c r="N3" s="172"/>
+      <c r="O3" s="168"/>
+      <c r="P3" s="169" t="s">
         <v>160</v>
       </c>
-      <c r="Q3" s="169"/>
-      <c r="R3" s="169"/>
-      <c r="S3" s="169"/>
-      <c r="T3" s="170"/>
+      <c r="Q3" s="170"/>
+      <c r="R3" s="170"/>
+      <c r="S3" s="170"/>
+      <c r="T3" s="171"/>
     </row>
     <row r="4" spans="1:22" s="44" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="H4" s="166" t="s">
+      <c r="H4" s="167" t="s">
         <v>66</v>
       </c>
-      <c r="I4" s="167"/>
-      <c r="J4" s="168" t="s">
+      <c r="I4" s="168"/>
+      <c r="J4" s="169" t="s">
         <v>175</v>
       </c>
-      <c r="K4" s="169"/>
-      <c r="L4" s="170"/>
-      <c r="M4" s="166" t="s">
+      <c r="K4" s="170"/>
+      <c r="L4" s="171"/>
+      <c r="M4" s="167" t="s">
         <v>77</v>
       </c>
-      <c r="N4" s="171"/>
-      <c r="O4" s="167"/>
-      <c r="P4" s="168" t="s">
+      <c r="N4" s="172"/>
+      <c r="O4" s="168"/>
+      <c r="P4" s="169" t="s">
         <v>176</v>
       </c>
-      <c r="Q4" s="169"/>
-      <c r="R4" s="169"/>
-      <c r="S4" s="169"/>
-      <c r="T4" s="170"/>
+      <c r="Q4" s="170"/>
+      <c r="R4" s="170"/>
+      <c r="S4" s="170"/>
+      <c r="T4" s="171"/>
     </row>
     <row r="5" spans="1:22" s="44" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="H5" s="166" t="s">
+      <c r="H5" s="167" t="s">
         <v>67</v>
       </c>
-      <c r="I5" s="167"/>
-      <c r="J5" s="168" t="s">
+      <c r="I5" s="168"/>
+      <c r="J5" s="169" t="s">
         <v>177</v>
       </c>
-      <c r="K5" s="169"/>
-      <c r="L5" s="170"/>
-      <c r="M5" s="166" t="s">
+      <c r="K5" s="170"/>
+      <c r="L5" s="171"/>
+      <c r="M5" s="167" t="s">
         <v>79</v>
       </c>
-      <c r="N5" s="167"/>
+      <c r="N5" s="168"/>
       <c r="O5" s="59" t="s">
         <v>178</v>
       </c>
-      <c r="P5" s="168" t="s">
+      <c r="P5" s="169" t="s">
         <v>172</v>
       </c>
-      <c r="Q5" s="169"/>
-      <c r="R5" s="169"/>
-      <c r="S5" s="169"/>
-      <c r="T5" s="170"/>
+      <c r="Q5" s="170"/>
+      <c r="R5" s="170"/>
+      <c r="S5" s="170"/>
+      <c r="T5" s="171"/>
     </row>
     <row r="6" spans="1:22" s="44" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="H6" s="166" t="s">
+      <c r="H6" s="167" t="s">
         <v>33</v>
       </c>
-      <c r="I6" s="167"/>
-      <c r="J6" s="166" t="s">
+      <c r="I6" s="168"/>
+      <c r="J6" s="167" t="s">
         <v>65</v>
       </c>
-      <c r="K6" s="171"/>
-      <c r="L6" s="167"/>
-      <c r="M6" s="166" t="s">
+      <c r="K6" s="172"/>
+      <c r="L6" s="168"/>
+      <c r="M6" s="167" t="s">
         <v>80</v>
       </c>
-      <c r="N6" s="167"/>
+      <c r="N6" s="168"/>
       <c r="O6" s="59" t="s">
         <v>179</v>
       </c>
-      <c r="P6" s="168" t="s">
+      <c r="P6" s="169" t="s">
         <v>173</v>
       </c>
-      <c r="Q6" s="169"/>
-      <c r="R6" s="169"/>
-      <c r="S6" s="169"/>
-      <c r="T6" s="170"/>
+      <c r="Q6" s="170"/>
+      <c r="R6" s="170"/>
+      <c r="S6" s="170"/>
+      <c r="T6" s="171"/>
     </row>
     <row r="7" spans="1:22" s="44" customFormat="1" ht="11.25" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="P7" s="104"/>
@@ -11282,12 +11282,12 @@
       <c r="A9" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B9" s="150" t="str">
+      <c r="B9" s="151" t="str">
         <f>'A-1'!B9:D9</f>
         <v>(令和9年04月)</v>
       </c>
-      <c r="C9" s="150"/>
-      <c r="D9" s="151"/>
+      <c r="C9" s="151"/>
+      <c r="D9" s="152"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -11297,28 +11297,28 @@
         <v>0</v>
       </c>
       <c r="B10" s="75"/>
-      <c r="C10" s="161" t="s">
+      <c r="C10" s="162" t="s">
         <v>56</v>
       </c>
-      <c r="D10" s="162"/>
-      <c r="E10" s="162"/>
-      <c r="F10" s="162"/>
-      <c r="G10" s="162"/>
-      <c r="H10" s="162"/>
+      <c r="D10" s="163"/>
+      <c r="E10" s="163"/>
+      <c r="F10" s="163"/>
+      <c r="G10" s="163"/>
+      <c r="H10" s="163"/>
       <c r="I10" s="75"/>
-      <c r="J10" s="163" t="s">
+      <c r="J10" s="164" t="s">
         <v>81</v>
       </c>
-      <c r="K10" s="164"/>
-      <c r="L10" s="164"/>
-      <c r="M10" s="164"/>
-      <c r="N10" s="164"/>
-      <c r="O10" s="164"/>
-      <c r="P10" s="164"/>
-      <c r="Q10" s="164"/>
-      <c r="R10" s="164"/>
-      <c r="S10" s="164"/>
-      <c r="T10" s="165"/>
+      <c r="K10" s="165"/>
+      <c r="L10" s="165"/>
+      <c r="M10" s="165"/>
+      <c r="N10" s="165"/>
+      <c r="O10" s="165"/>
+      <c r="P10" s="165"/>
+      <c r="Q10" s="165"/>
+      <c r="R10" s="165"/>
+      <c r="S10" s="165"/>
+      <c r="T10" s="166"/>
     </row>
     <row r="11" spans="1:22" s="44" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="77"/>
@@ -11352,19 +11352,19 @@
       <c r="K11" s="79" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="163" t="s">
+      <c r="L11" s="164" t="s">
         <v>62</v>
       </c>
-      <c r="M11" s="164"/>
-      <c r="N11" s="164"/>
-      <c r="O11" s="164"/>
-      <c r="P11" s="163" t="s">
+      <c r="M11" s="165"/>
+      <c r="N11" s="165"/>
+      <c r="O11" s="165"/>
+      <c r="P11" s="164" t="s">
         <v>63</v>
       </c>
-      <c r="Q11" s="164"/>
-      <c r="R11" s="164"/>
-      <c r="S11" s="164"/>
-      <c r="T11" s="165"/>
+      <c r="Q11" s="165"/>
+      <c r="R11" s="165"/>
+      <c r="S11" s="165"/>
+      <c r="T11" s="166"/>
     </row>
     <row r="12" spans="1:22" s="44" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="77"/>
@@ -13333,39 +13333,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" s="107" customFormat="1" ht="18.75" x14ac:dyDescent="0.15">
-      <c r="A1" s="172" t="s">
+      <c r="A1" s="173" t="s">
         <v>138</v>
       </c>
-      <c r="B1" s="172"/>
-      <c r="C1" s="172"/>
-      <c r="D1" s="172"/>
-      <c r="E1" s="172"/>
-      <c r="F1" s="172"/>
-      <c r="G1" s="172"/>
-      <c r="H1" s="172"/>
-      <c r="I1" s="172"/>
-      <c r="J1" s="172"/>
-      <c r="K1" s="172"/>
-      <c r="L1" s="172"/>
-      <c r="M1" s="172"/>
-      <c r="N1" s="172"/>
-      <c r="O1" s="172"/>
-      <c r="P1" s="172"/>
-      <c r="Q1" s="172"/>
-      <c r="R1" s="172"/>
-      <c r="S1" s="172"/>
-      <c r="T1" s="172"/>
-      <c r="U1" s="172"/>
-      <c r="V1" s="172"/>
-      <c r="W1" s="172"/>
-      <c r="X1" s="172"/>
-      <c r="Y1" s="172"/>
-      <c r="Z1" s="172"/>
-      <c r="AA1" s="172"/>
-      <c r="AB1" s="172"/>
-      <c r="AC1" s="172"/>
-      <c r="AD1" s="172"/>
-      <c r="AE1" s="172"/>
+      <c r="B1" s="173"/>
+      <c r="C1" s="173"/>
+      <c r="D1" s="173"/>
+      <c r="E1" s="173"/>
+      <c r="F1" s="173"/>
+      <c r="G1" s="173"/>
+      <c r="H1" s="173"/>
+      <c r="I1" s="173"/>
+      <c r="J1" s="173"/>
+      <c r="K1" s="173"/>
+      <c r="L1" s="173"/>
+      <c r="M1" s="173"/>
+      <c r="N1" s="173"/>
+      <c r="O1" s="173"/>
+      <c r="P1" s="173"/>
+      <c r="Q1" s="173"/>
+      <c r="R1" s="173"/>
+      <c r="S1" s="173"/>
+      <c r="T1" s="173"/>
+      <c r="U1" s="173"/>
+      <c r="V1" s="173"/>
+      <c r="W1" s="173"/>
+      <c r="X1" s="173"/>
+      <c r="Y1" s="173"/>
+      <c r="Z1" s="173"/>
+      <c r="AA1" s="173"/>
+      <c r="AB1" s="173"/>
+      <c r="AC1" s="173"/>
+      <c r="AD1" s="173"/>
+      <c r="AE1" s="173"/>
     </row>
     <row r="2" spans="1:31" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="3" spans="1:31" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -13375,104 +13375,104 @@
     <row r="7" spans="1:31" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="8" spans="1:31" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="9" spans="1:31" s="107" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="176" t="str">
+      <c r="B9" s="177" t="str">
         <f>'A-1'!B9:D9</f>
         <v>(令和9年04月)</v>
       </c>
-      <c r="C9" s="176"/>
-      <c r="D9" s="177"/>
+      <c r="C9" s="177"/>
+      <c r="D9" s="178"/>
     </row>
     <row r="10" spans="1:31" s="107" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="109"/>
-      <c r="B10" s="173" t="s">
+      <c r="B10" s="174" t="s">
         <v>82</v>
       </c>
-      <c r="C10" s="174"/>
-      <c r="D10" s="174"/>
-      <c r="E10" s="174"/>
-      <c r="F10" s="175"/>
-      <c r="G10" s="173" t="s">
+      <c r="C10" s="175"/>
+      <c r="D10" s="175"/>
+      <c r="E10" s="175"/>
+      <c r="F10" s="176"/>
+      <c r="G10" s="174" t="s">
         <v>82</v>
       </c>
-      <c r="H10" s="174"/>
-      <c r="I10" s="174"/>
-      <c r="J10" s="174"/>
-      <c r="K10" s="175"/>
-      <c r="L10" s="173" t="s">
+      <c r="H10" s="175"/>
+      <c r="I10" s="175"/>
+      <c r="J10" s="175"/>
+      <c r="K10" s="176"/>
+      <c r="L10" s="174" t="s">
         <v>82</v>
       </c>
-      <c r="M10" s="174"/>
-      <c r="N10" s="174"/>
-      <c r="O10" s="174"/>
-      <c r="P10" s="175"/>
-      <c r="Q10" s="173" t="s">
+      <c r="M10" s="175"/>
+      <c r="N10" s="175"/>
+      <c r="O10" s="175"/>
+      <c r="P10" s="176"/>
+      <c r="Q10" s="174" t="s">
         <v>82</v>
       </c>
-      <c r="R10" s="174"/>
-      <c r="S10" s="174"/>
-      <c r="T10" s="174"/>
-      <c r="U10" s="175"/>
-      <c r="V10" s="173" t="s">
+      <c r="R10" s="175"/>
+      <c r="S10" s="175"/>
+      <c r="T10" s="175"/>
+      <c r="U10" s="176"/>
+      <c r="V10" s="174" t="s">
         <v>82</v>
       </c>
-      <c r="W10" s="174"/>
-      <c r="X10" s="174"/>
-      <c r="Y10" s="174"/>
-      <c r="Z10" s="175"/>
-      <c r="AA10" s="173" t="s">
+      <c r="W10" s="175"/>
+      <c r="X10" s="175"/>
+      <c r="Y10" s="175"/>
+      <c r="Z10" s="176"/>
+      <c r="AA10" s="174" t="s">
         <v>82</v>
       </c>
-      <c r="AB10" s="174"/>
-      <c r="AC10" s="174"/>
-      <c r="AD10" s="174"/>
-      <c r="AE10" s="175"/>
+      <c r="AB10" s="175"/>
+      <c r="AC10" s="175"/>
+      <c r="AD10" s="175"/>
+      <c r="AE10" s="176"/>
     </row>
     <row r="11" spans="1:31" s="107" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="110" t="s">
         <v>83</v>
       </c>
-      <c r="B11" s="173" t="s">
+      <c r="B11" s="174" t="s">
         <v>94</v>
       </c>
-      <c r="C11" s="174"/>
-      <c r="D11" s="174"/>
-      <c r="E11" s="174"/>
-      <c r="F11" s="175"/>
-      <c r="G11" s="173" t="s">
+      <c r="C11" s="175"/>
+      <c r="D11" s="175"/>
+      <c r="E11" s="175"/>
+      <c r="F11" s="176"/>
+      <c r="G11" s="174" t="s">
         <v>99</v>
       </c>
-      <c r="H11" s="174"/>
-      <c r="I11" s="174"/>
-      <c r="J11" s="174"/>
-      <c r="K11" s="175"/>
-      <c r="L11" s="173" t="s">
+      <c r="H11" s="175"/>
+      <c r="I11" s="175"/>
+      <c r="J11" s="175"/>
+      <c r="K11" s="176"/>
+      <c r="L11" s="174" t="s">
         <v>137</v>
       </c>
-      <c r="M11" s="174"/>
-      <c r="N11" s="174"/>
-      <c r="O11" s="174"/>
-      <c r="P11" s="175"/>
-      <c r="Q11" s="173" t="s">
+      <c r="M11" s="175"/>
+      <c r="N11" s="175"/>
+      <c r="O11" s="175"/>
+      <c r="P11" s="176"/>
+      <c r="Q11" s="174" t="s">
         <v>128</v>
       </c>
-      <c r="R11" s="174"/>
-      <c r="S11" s="174"/>
-      <c r="T11" s="174"/>
-      <c r="U11" s="175"/>
-      <c r="V11" s="178" t="s">
+      <c r="R11" s="175"/>
+      <c r="S11" s="175"/>
+      <c r="T11" s="175"/>
+      <c r="U11" s="176"/>
+      <c r="V11" s="179" t="s">
         <v>195</v>
       </c>
-      <c r="W11" s="179"/>
-      <c r="X11" s="179"/>
-      <c r="Y11" s="179"/>
-      <c r="Z11" s="180"/>
-      <c r="AA11" s="173" t="s">
+      <c r="W11" s="180"/>
+      <c r="X11" s="180"/>
+      <c r="Y11" s="180"/>
+      <c r="Z11" s="181"/>
+      <c r="AA11" s="174" t="s">
         <v>136</v>
       </c>
-      <c r="AB11" s="174"/>
-      <c r="AC11" s="174"/>
-      <c r="AD11" s="174"/>
-      <c r="AE11" s="175"/>
+      <c r="AB11" s="175"/>
+      <c r="AC11" s="175"/>
+      <c r="AD11" s="175"/>
+      <c r="AE11" s="176"/>
     </row>
     <row r="12" spans="1:31" s="113" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="111"/>
@@ -15386,30 +15386,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" s="107" customFormat="1" ht="18.75" x14ac:dyDescent="0.15">
-      <c r="A1" s="172" t="s">
+      <c r="A1" s="173" t="s">
         <v>156</v>
       </c>
-      <c r="B1" s="172"/>
-      <c r="C1" s="172"/>
-      <c r="D1" s="172"/>
-      <c r="E1" s="172"/>
-      <c r="F1" s="172"/>
-      <c r="G1" s="172"/>
-      <c r="H1" s="172"/>
-      <c r="I1" s="172"/>
-      <c r="J1" s="172"/>
-      <c r="K1" s="172"/>
-      <c r="L1" s="172"/>
-      <c r="M1" s="172"/>
-      <c r="N1" s="172"/>
-      <c r="O1" s="172"/>
-      <c r="P1" s="172"/>
-      <c r="Q1" s="172"/>
-      <c r="R1" s="172"/>
-      <c r="S1" s="172"/>
-      <c r="T1" s="172"/>
-      <c r="U1" s="172"/>
-      <c r="V1" s="172"/>
+      <c r="B1" s="173"/>
+      <c r="C1" s="173"/>
+      <c r="D1" s="173"/>
+      <c r="E1" s="173"/>
+      <c r="F1" s="173"/>
+      <c r="G1" s="173"/>
+      <c r="H1" s="173"/>
+      <c r="I1" s="173"/>
+      <c r="J1" s="173"/>
+      <c r="K1" s="173"/>
+      <c r="L1" s="173"/>
+      <c r="M1" s="173"/>
+      <c r="N1" s="173"/>
+      <c r="O1" s="173"/>
+      <c r="P1" s="173"/>
+      <c r="Q1" s="173"/>
+      <c r="R1" s="173"/>
+      <c r="S1" s="173"/>
+      <c r="T1" s="173"/>
+      <c r="U1" s="173"/>
+      <c r="V1" s="173"/>
     </row>
     <row r="2" spans="1:22" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="3" spans="1:22" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -15419,44 +15419,44 @@
     <row r="7" spans="1:22" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="8" spans="1:22" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="9" spans="1:22" s="107" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="184" t="str">
+      <c r="B9" s="185" t="str">
         <f>'A-1'!B9:D9</f>
         <v>(令和9年04月)</v>
       </c>
-      <c r="C9" s="184"/>
-      <c r="D9" s="185"/>
+      <c r="C9" s="185"/>
+      <c r="D9" s="186"/>
     </row>
     <row r="10" spans="1:22" s="107" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="115"/>
-      <c r="B10" s="186" t="s">
+      <c r="B10" s="187" t="s">
         <v>97</v>
       </c>
-      <c r="C10" s="187"/>
-      <c r="D10" s="187"/>
-      <c r="E10" s="187"/>
-      <c r="F10" s="188"/>
-      <c r="G10" s="186" t="s">
+      <c r="C10" s="188"/>
+      <c r="D10" s="188"/>
+      <c r="E10" s="188"/>
+      <c r="F10" s="189"/>
+      <c r="G10" s="187" t="s">
         <v>98</v>
       </c>
-      <c r="H10" s="187"/>
-      <c r="I10" s="187"/>
-      <c r="J10" s="187"/>
-      <c r="K10" s="188"/>
+      <c r="H10" s="188"/>
+      <c r="I10" s="188"/>
+      <c r="J10" s="188"/>
+      <c r="K10" s="189"/>
       <c r="L10" s="115"/>
-      <c r="M10" s="181" t="s">
+      <c r="M10" s="182" t="s">
         <v>157</v>
       </c>
-      <c r="N10" s="182"/>
-      <c r="O10" s="182"/>
-      <c r="P10" s="182"/>
-      <c r="Q10" s="183"/>
-      <c r="R10" s="181" t="s">
+      <c r="N10" s="183"/>
+      <c r="O10" s="183"/>
+      <c r="P10" s="183"/>
+      <c r="Q10" s="184"/>
+      <c r="R10" s="182" t="s">
         <v>158</v>
       </c>
-      <c r="S10" s="182"/>
-      <c r="T10" s="182"/>
-      <c r="U10" s="182"/>
-      <c r="V10" s="183"/>
+      <c r="S10" s="183"/>
+      <c r="T10" s="183"/>
+      <c r="U10" s="183"/>
+      <c r="V10" s="184"/>
     </row>
     <row r="11" spans="1:22" s="120" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="118" t="s">
@@ -16894,34 +16894,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18.75" x14ac:dyDescent="0.15">
-      <c r="A1" s="192" t="s">
+      <c r="A1" s="193" t="s">
         <v>155</v>
       </c>
-      <c r="B1" s="192"/>
-      <c r="C1" s="192"/>
-      <c r="D1" s="192"/>
-      <c r="E1" s="192"/>
-      <c r="F1" s="192"/>
-      <c r="G1" s="192"/>
-      <c r="H1" s="192"/>
-      <c r="I1" s="192"/>
-      <c r="J1" s="192"/>
-      <c r="K1" s="192"/>
-      <c r="L1" s="192"/>
-      <c r="M1" s="192"/>
-      <c r="N1" s="192"/>
-      <c r="O1" s="192"/>
-      <c r="P1" s="192"/>
-      <c r="Q1" s="192"/>
-      <c r="R1" s="192"/>
-      <c r="S1" s="192"/>
-      <c r="T1" s="192"/>
-      <c r="U1" s="192"/>
-      <c r="V1" s="192"/>
-      <c r="W1" s="192"/>
-      <c r="X1" s="192"/>
-      <c r="Y1" s="192"/>
-      <c r="Z1" s="192"/>
+      <c r="B1" s="193"/>
+      <c r="C1" s="193"/>
+      <c r="D1" s="193"/>
+      <c r="E1" s="193"/>
+      <c r="F1" s="193"/>
+      <c r="G1" s="193"/>
+      <c r="H1" s="193"/>
+      <c r="I1" s="193"/>
+      <c r="J1" s="193"/>
+      <c r="K1" s="193"/>
+      <c r="L1" s="193"/>
+      <c r="M1" s="193"/>
+      <c r="N1" s="193"/>
+      <c r="O1" s="193"/>
+      <c r="P1" s="193"/>
+      <c r="Q1" s="193"/>
+      <c r="R1" s="193"/>
+      <c r="S1" s="193"/>
+      <c r="T1" s="193"/>
+      <c r="U1" s="193"/>
+      <c r="V1" s="193"/>
+      <c r="W1" s="193"/>
+      <c r="X1" s="193"/>
+      <c r="Y1" s="193"/>
+      <c r="Z1" s="193"/>
     </row>
     <row r="2" spans="1:26" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="3" spans="1:26" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -16931,50 +16931,50 @@
     <row r="7" spans="1:26" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="8" spans="1:26" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="9" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="150" t="str">
+      <c r="B9" s="151" t="str">
         <f>'A-1'!B9:D9</f>
         <v>(令和9年04月)</v>
       </c>
-      <c r="C9" s="150"/>
-      <c r="D9" s="151"/>
+      <c r="C9" s="151"/>
+      <c r="D9" s="152"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="102"/>
-      <c r="B10" s="189" t="s">
+      <c r="B10" s="190" t="s">
         <v>95</v>
       </c>
-      <c r="C10" s="190"/>
-      <c r="D10" s="190"/>
-      <c r="E10" s="190"/>
-      <c r="F10" s="191"/>
-      <c r="G10" s="189" t="s">
+      <c r="C10" s="191"/>
+      <c r="D10" s="191"/>
+      <c r="E10" s="191"/>
+      <c r="F10" s="192"/>
+      <c r="G10" s="190" t="s">
         <v>96</v>
       </c>
-      <c r="H10" s="190"/>
-      <c r="I10" s="190"/>
-      <c r="J10" s="190"/>
-      <c r="K10" s="191"/>
-      <c r="L10" s="189" t="s">
+      <c r="H10" s="191"/>
+      <c r="I10" s="191"/>
+      <c r="J10" s="191"/>
+      <c r="K10" s="192"/>
+      <c r="L10" s="190" t="s">
         <v>139</v>
       </c>
-      <c r="M10" s="190"/>
-      <c r="N10" s="190"/>
-      <c r="O10" s="190"/>
-      <c r="P10" s="191"/>
-      <c r="Q10" s="189" t="s">
+      <c r="M10" s="191"/>
+      <c r="N10" s="191"/>
+      <c r="O10" s="191"/>
+      <c r="P10" s="192"/>
+      <c r="Q10" s="190" t="s">
         <v>154</v>
       </c>
-      <c r="R10" s="190"/>
-      <c r="S10" s="190"/>
-      <c r="T10" s="190"/>
-      <c r="U10" s="191"/>
-      <c r="V10" s="189" t="s">
+      <c r="R10" s="191"/>
+      <c r="S10" s="191"/>
+      <c r="T10" s="191"/>
+      <c r="U10" s="192"/>
+      <c r="V10" s="190" t="s">
         <v>140</v>
       </c>
-      <c r="W10" s="190"/>
-      <c r="X10" s="190"/>
-      <c r="Y10" s="190"/>
-      <c r="Z10" s="191"/>
+      <c r="W10" s="191"/>
+      <c r="X10" s="191"/>
+      <c r="Y10" s="191"/>
+      <c r="Z10" s="192"/>
     </row>
     <row r="11" spans="1:26" s="40" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="47" t="s">
@@ -18588,30 +18588,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="18.75" x14ac:dyDescent="0.15">
-      <c r="A1" s="192" t="s">
+      <c r="A1" s="193" t="s">
         <v>150</v>
       </c>
-      <c r="B1" s="192"/>
-      <c r="C1" s="192"/>
-      <c r="D1" s="192"/>
-      <c r="E1" s="192"/>
-      <c r="F1" s="192"/>
-      <c r="G1" s="192"/>
-      <c r="H1" s="192"/>
-      <c r="I1" s="192"/>
-      <c r="J1" s="192"/>
-      <c r="K1" s="192"/>
-      <c r="L1" s="192"/>
-      <c r="M1" s="192"/>
-      <c r="N1" s="192"/>
-      <c r="O1" s="192"/>
-      <c r="P1" s="192"/>
-      <c r="Q1" s="192"/>
-      <c r="R1" s="192"/>
-      <c r="S1" s="192"/>
-      <c r="T1" s="192"/>
-      <c r="U1" s="192"/>
-      <c r="V1" s="192"/>
+      <c r="B1" s="193"/>
+      <c r="C1" s="193"/>
+      <c r="D1" s="193"/>
+      <c r="E1" s="193"/>
+      <c r="F1" s="193"/>
+      <c r="G1" s="193"/>
+      <c r="H1" s="193"/>
+      <c r="I1" s="193"/>
+      <c r="J1" s="193"/>
+      <c r="K1" s="193"/>
+      <c r="L1" s="193"/>
+      <c r="M1" s="193"/>
+      <c r="N1" s="193"/>
+      <c r="O1" s="193"/>
+      <c r="P1" s="193"/>
+      <c r="Q1" s="193"/>
+      <c r="R1" s="193"/>
+      <c r="S1" s="193"/>
+      <c r="T1" s="193"/>
+      <c r="U1" s="193"/>
+      <c r="V1" s="193"/>
     </row>
     <row r="2" spans="1:22" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="3" spans="1:22" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -18621,44 +18621,44 @@
     <row r="7" spans="1:22" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="8" spans="1:22" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="9" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="150" t="str">
+      <c r="B9" s="151" t="str">
         <f>'A-1'!B9:D9</f>
         <v>(令和9年04月)</v>
       </c>
-      <c r="C9" s="150"/>
-      <c r="D9" s="151"/>
+      <c r="C9" s="151"/>
+      <c r="D9" s="152"/>
     </row>
     <row r="10" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="102"/>
-      <c r="B10" s="189" t="s">
+      <c r="B10" s="190" t="s">
         <v>149</v>
       </c>
-      <c r="C10" s="190"/>
-      <c r="D10" s="190"/>
-      <c r="E10" s="190"/>
-      <c r="F10" s="191"/>
-      <c r="G10" s="189" t="s">
+      <c r="C10" s="191"/>
+      <c r="D10" s="191"/>
+      <c r="E10" s="191"/>
+      <c r="F10" s="192"/>
+      <c r="G10" s="190" t="s">
         <v>151</v>
       </c>
-      <c r="H10" s="190"/>
-      <c r="I10" s="190"/>
-      <c r="J10" s="190"/>
-      <c r="K10" s="191"/>
+      <c r="H10" s="191"/>
+      <c r="I10" s="191"/>
+      <c r="J10" s="191"/>
+      <c r="K10" s="192"/>
       <c r="L10" s="102"/>
-      <c r="M10" s="189" t="s">
+      <c r="M10" s="190" t="s">
         <v>152</v>
       </c>
-      <c r="N10" s="190"/>
-      <c r="O10" s="190"/>
-      <c r="P10" s="190"/>
-      <c r="Q10" s="191"/>
-      <c r="R10" s="189" t="s">
+      <c r="N10" s="191"/>
+      <c r="O10" s="191"/>
+      <c r="P10" s="191"/>
+      <c r="Q10" s="192"/>
+      <c r="R10" s="190" t="s">
         <v>153</v>
       </c>
-      <c r="S10" s="190"/>
-      <c r="T10" s="190"/>
-      <c r="U10" s="190"/>
-      <c r="V10" s="191"/>
+      <c r="S10" s="191"/>
+      <c r="T10" s="191"/>
+      <c r="U10" s="191"/>
+      <c r="V10" s="192"/>
     </row>
     <row r="11" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="47" t="s">
@@ -20098,30 +20098,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="18.75" x14ac:dyDescent="0.15">
-      <c r="A1" s="192" t="s">
+      <c r="A1" s="193" t="s">
         <v>144</v>
       </c>
-      <c r="B1" s="192"/>
-      <c r="C1" s="192"/>
-      <c r="D1" s="192"/>
-      <c r="E1" s="192"/>
-      <c r="F1" s="192"/>
-      <c r="G1" s="192"/>
-      <c r="H1" s="192"/>
-      <c r="I1" s="192"/>
-      <c r="J1" s="192"/>
-      <c r="K1" s="192"/>
-      <c r="L1" s="192"/>
-      <c r="M1" s="192"/>
-      <c r="N1" s="192"/>
-      <c r="O1" s="192"/>
-      <c r="P1" s="192"/>
-      <c r="Q1" s="192"/>
-      <c r="R1" s="192"/>
-      <c r="S1" s="192"/>
-      <c r="T1" s="192"/>
-      <c r="U1" s="192"/>
-      <c r="V1" s="192"/>
+      <c r="B1" s="193"/>
+      <c r="C1" s="193"/>
+      <c r="D1" s="193"/>
+      <c r="E1" s="193"/>
+      <c r="F1" s="193"/>
+      <c r="G1" s="193"/>
+      <c r="H1" s="193"/>
+      <c r="I1" s="193"/>
+      <c r="J1" s="193"/>
+      <c r="K1" s="193"/>
+      <c r="L1" s="193"/>
+      <c r="M1" s="193"/>
+      <c r="N1" s="193"/>
+      <c r="O1" s="193"/>
+      <c r="P1" s="193"/>
+      <c r="Q1" s="193"/>
+      <c r="R1" s="193"/>
+      <c r="S1" s="193"/>
+      <c r="T1" s="193"/>
+      <c r="U1" s="193"/>
+      <c r="V1" s="193"/>
     </row>
     <row r="2" spans="1:22" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="3" spans="1:22" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -20131,44 +20131,44 @@
     <row r="7" spans="1:22" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="8" spans="1:22" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="9" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="150" t="str">
+      <c r="B9" s="151" t="str">
         <f>'A-1'!B9:D9</f>
         <v>(令和9年04月)</v>
       </c>
-      <c r="C9" s="150"/>
-      <c r="D9" s="151"/>
+      <c r="C9" s="151"/>
+      <c r="D9" s="152"/>
     </row>
     <row r="10" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="102"/>
-      <c r="B10" s="189" t="s">
+      <c r="B10" s="190" t="s">
         <v>112</v>
       </c>
-      <c r="C10" s="190"/>
-      <c r="D10" s="190"/>
-      <c r="E10" s="190"/>
-      <c r="F10" s="191"/>
-      <c r="G10" s="189" t="s">
+      <c r="C10" s="191"/>
+      <c r="D10" s="191"/>
+      <c r="E10" s="191"/>
+      <c r="F10" s="192"/>
+      <c r="G10" s="190" t="s">
         <v>115</v>
       </c>
-      <c r="H10" s="190"/>
-      <c r="I10" s="190"/>
-      <c r="J10" s="190"/>
-      <c r="K10" s="191"/>
+      <c r="H10" s="191"/>
+      <c r="I10" s="191"/>
+      <c r="J10" s="191"/>
+      <c r="K10" s="192"/>
       <c r="L10" s="102"/>
-      <c r="M10" s="189" t="s">
+      <c r="M10" s="190" t="s">
         <v>113</v>
       </c>
-      <c r="N10" s="190"/>
-      <c r="O10" s="190"/>
-      <c r="P10" s="190"/>
-      <c r="Q10" s="191"/>
-      <c r="R10" s="189" t="s">
+      <c r="N10" s="191"/>
+      <c r="O10" s="191"/>
+      <c r="P10" s="191"/>
+      <c r="Q10" s="192"/>
+      <c r="R10" s="190" t="s">
         <v>114</v>
       </c>
-      <c r="S10" s="190"/>
-      <c r="T10" s="190"/>
-      <c r="U10" s="190"/>
-      <c r="V10" s="191"/>
+      <c r="S10" s="191"/>
+      <c r="T10" s="191"/>
+      <c r="U10" s="191"/>
+      <c r="V10" s="192"/>
     </row>
     <row r="11" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="47" t="s">
@@ -21608,30 +21608,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="18.75" x14ac:dyDescent="0.15">
-      <c r="A1" s="192" t="s">
+      <c r="A1" s="193" t="s">
         <v>190</v>
       </c>
-      <c r="B1" s="192"/>
-      <c r="C1" s="192"/>
-      <c r="D1" s="192"/>
-      <c r="E1" s="192"/>
-      <c r="F1" s="192"/>
-      <c r="G1" s="192"/>
-      <c r="H1" s="192"/>
-      <c r="I1" s="192"/>
-      <c r="J1" s="192"/>
-      <c r="K1" s="192"/>
-      <c r="L1" s="192"/>
-      <c r="M1" s="192"/>
-      <c r="N1" s="192"/>
-      <c r="O1" s="192"/>
-      <c r="P1" s="192"/>
-      <c r="Q1" s="192"/>
-      <c r="R1" s="192"/>
-      <c r="S1" s="192"/>
-      <c r="T1" s="192"/>
-      <c r="U1" s="192"/>
-      <c r="V1" s="192"/>
+      <c r="B1" s="193"/>
+      <c r="C1" s="193"/>
+      <c r="D1" s="193"/>
+      <c r="E1" s="193"/>
+      <c r="F1" s="193"/>
+      <c r="G1" s="193"/>
+      <c r="H1" s="193"/>
+      <c r="I1" s="193"/>
+      <c r="J1" s="193"/>
+      <c r="K1" s="193"/>
+      <c r="L1" s="193"/>
+      <c r="M1" s="193"/>
+      <c r="N1" s="193"/>
+      <c r="O1" s="193"/>
+      <c r="P1" s="193"/>
+      <c r="Q1" s="193"/>
+      <c r="R1" s="193"/>
+      <c r="S1" s="193"/>
+      <c r="T1" s="193"/>
+      <c r="U1" s="193"/>
+      <c r="V1" s="193"/>
     </row>
     <row r="2" spans="1:22" hidden="1" x14ac:dyDescent="0.15"/>
     <row r="3" spans="1:22" hidden="1" x14ac:dyDescent="0.15"/>
@@ -21641,44 +21641,44 @@
     <row r="7" spans="1:22" hidden="1" x14ac:dyDescent="0.15"/>
     <row r="8" spans="1:22" hidden="1" x14ac:dyDescent="0.15"/>
     <row r="9" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="150" t="str">
+      <c r="B9" s="151" t="str">
         <f>'A-1'!B9:D9</f>
         <v>(令和9年04月)</v>
       </c>
-      <c r="C9" s="150"/>
-      <c r="D9" s="151"/>
+      <c r="C9" s="151"/>
+      <c r="D9" s="152"/>
     </row>
     <row r="10" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="102"/>
-      <c r="B10" s="189" t="s">
+      <c r="B10" s="190" t="s">
         <v>191</v>
       </c>
-      <c r="C10" s="190"/>
-      <c r="D10" s="190"/>
-      <c r="E10" s="190"/>
-      <c r="F10" s="191"/>
-      <c r="G10" s="189" t="s">
+      <c r="C10" s="191"/>
+      <c r="D10" s="191"/>
+      <c r="E10" s="191"/>
+      <c r="F10" s="192"/>
+      <c r="G10" s="190" t="s">
         <v>192</v>
       </c>
-      <c r="H10" s="190"/>
-      <c r="I10" s="190"/>
-      <c r="J10" s="190"/>
-      <c r="K10" s="191"/>
+      <c r="H10" s="191"/>
+      <c r="I10" s="191"/>
+      <c r="J10" s="191"/>
+      <c r="K10" s="192"/>
       <c r="L10" s="102"/>
-      <c r="M10" s="189" t="s">
+      <c r="M10" s="190" t="s">
         <v>193</v>
       </c>
-      <c r="N10" s="190"/>
-      <c r="O10" s="190"/>
-      <c r="P10" s="190"/>
-      <c r="Q10" s="191"/>
-      <c r="R10" s="189" t="s">
+      <c r="N10" s="191"/>
+      <c r="O10" s="191"/>
+      <c r="P10" s="191"/>
+      <c r="Q10" s="192"/>
+      <c r="R10" s="190" t="s">
         <v>194</v>
       </c>
-      <c r="S10" s="190"/>
-      <c r="T10" s="190"/>
-      <c r="U10" s="190"/>
-      <c r="V10" s="191"/>
+      <c r="S10" s="191"/>
+      <c r="T10" s="191"/>
+      <c r="U10" s="191"/>
+      <c r="V10" s="192"/>
     </row>
     <row r="11" spans="1:22" s="40" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
